--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/kd/KD 발주 2026-02.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/kd/KD 발주 2026-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,6 +429,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>납기</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>재고</t>
         </is>
       </c>
@@ -440,42 +445,51 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
+      </c>
+      <c r="D2" t="n">
+        <v>339</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>880</v>
+        <v>666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
+      </c>
+      <c r="D3" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>963</v>
+        <v>869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
+      </c>
+      <c r="D4" t="n">
+        <v>423</v>
       </c>
     </row>
     <row r="5">
@@ -485,243 +499,291 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>302</v>
+        <v>923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
+      </c>
+      <c r="D5" t="n">
+        <v>313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
+      </c>
+      <c r="D6" t="n">
+        <v>329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
+      </c>
+      <c r="D7" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>725</v>
+        <v>882</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
+      </c>
+      <c r="D8" t="n">
+        <v>253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>639</v>
+        <v>86</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
+      </c>
+      <c r="D9" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>700</v>
+        <v>338</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
+      </c>
+      <c r="D10" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>680</v>
+        <v>238</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
+      </c>
+      <c r="D12" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>171</v>
+        <v>397</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
+      </c>
+      <c r="D13" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>292</v>
+        <v>90</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
+      </c>
+      <c r="D14" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>371</v>
+        <v>830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
+      </c>
+      <c r="D15" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>414</v>
+        <v>100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
+      </c>
+      <c r="D16" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>610</v>
+        <v>467</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
+      </c>
+      <c r="D17" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
+      </c>
+      <c r="D18" t="n">
+        <v>381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>764</v>
+        <v>28</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
+      </c>
+      <c r="D19" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -732,335 +794,404 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>753</v>
+        <v>820</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
+      </c>
+      <c r="D22" t="n">
+        <v>309</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>946</v>
+        <v>662</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
+      </c>
+      <c r="D23" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>366</v>
+        <v>585</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
+      </c>
+      <c r="D24" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>996</v>
+        <v>697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
+      </c>
+      <c r="D25" t="n">
+        <v>233</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>241</v>
+        <v>382</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
+      </c>
+      <c r="D26" t="n">
+        <v>422</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>996</v>
+        <v>846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
+      </c>
+      <c r="D27" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>475</v>
+        <v>349</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
+      </c>
+      <c r="D28" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
+      </c>
+      <c r="D29" t="n">
+        <v>242</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>277</v>
+        <v>682</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
+      </c>
+      <c r="D30" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>426</v>
+        <v>473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
+      </c>
+      <c r="D31" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>119</v>
+        <v>787</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
+      </c>
+      <c r="D32" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
+      </c>
+      <c r="D33" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>311</v>
+        <v>859</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
+      </c>
+      <c r="D34" t="n">
+        <v>324</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>979</v>
+        <v>570</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
+      </c>
+      <c r="D35" t="n">
+        <v>267</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>832</v>
+        <v>728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
+      </c>
+      <c r="D36" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>989</v>
+        <v>928</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
+      </c>
+      <c r="D37" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>907</v>
+        <v>153</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
+      </c>
+      <c r="D38" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>842</v>
+        <v>770</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
+      </c>
+      <c r="D39" t="n">
+        <v>369</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>266</v>
+        <v>119</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
+      </c>
+      <c r="D40" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>463</v>
+        <v>210</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
+      </c>
+      <c r="D41" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>586</v>
+        <v>962</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
+      </c>
+      <c r="D42" t="n">
+        <v>436</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>798</v>
+        <v>230</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
+      </c>
+      <c r="D43" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="44">
@@ -1070,282 +1201,339 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>785</v>
+        <v>743</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
+      </c>
+      <c r="D44" t="n">
+        <v>173</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>994</v>
+        <v>785</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
+      </c>
+      <c r="D45" t="n">
+        <v>212</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>707</v>
+        <v>958</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
+      </c>
+      <c r="D46" t="n">
+        <v>324</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>928</v>
+        <v>612</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
+      </c>
+      <c r="D47" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>892</v>
+        <v>478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
+      </c>
+      <c r="D48" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>503</v>
+        <v>989</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
+      </c>
+      <c r="D49" t="n">
+        <v>258</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>274</v>
+        <v>996</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
+      </c>
+      <c r="D50" t="n">
+        <v>255</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>401</v>
+        <v>553</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
+      </c>
+      <c r="D51" t="n">
+        <v>376</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>817</v>
+        <v>576</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
+      </c>
+      <c r="D52" t="n">
+        <v>478</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>703</v>
+        <v>868</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
+      </c>
+      <c r="D53" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>245</v>
+        <v>956</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
+      </c>
+      <c r="D54" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>432</v>
+        <v>718</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
+      </c>
+      <c r="D55" t="n">
+        <v>296</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>538</v>
+        <v>758</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
+      </c>
+      <c r="D56" t="n">
+        <v>417</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
+      </c>
+      <c r="D57" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>862</v>
+        <v>624</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
+      </c>
+      <c r="D58" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>264</v>
+        <v>526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
+      </c>
+      <c r="D59" t="n">
+        <v>451</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>105</v>
+        <v>438</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
+      </c>
+      <c r="D60" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>699</v>
+        <v>790</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
+      </c>
+      <c r="D61" t="n">
+        <v>127</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>850</v>
+        <v>417</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
+      </c>
+      <c r="D62" t="n">
+        <v>493</v>
       </c>
     </row>
     <row r="63">
@@ -1355,222 +1543,267 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>87</v>
+        <v>311</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
+      </c>
+      <c r="D63" t="n">
+        <v>231</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>963</v>
+        <v>151</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
+      </c>
+      <c r="D64" t="n">
+        <v>211</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>497</v>
+        <v>726</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
+      </c>
+      <c r="D65" t="n">
+        <v>453</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>372</v>
+        <v>534</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
+      </c>
+      <c r="D66" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>925</v>
+        <v>570</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
+      </c>
+      <c r="D67" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>285</v>
+        <v>738</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
+      </c>
+      <c r="D68" t="n">
+        <v>377</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>979</v>
+        <v>657</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
+      </c>
+      <c r="D69" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>709</v>
+        <v>224</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
+      </c>
+      <c r="D70" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>520</v>
+        <v>307</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
+      </c>
+      <c r="D71" t="n">
+        <v>351</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>214</v>
+        <v>953</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
+      </c>
+      <c r="D72" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>763</v>
+        <v>737</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
+      </c>
+      <c r="D73" t="n">
+        <v>332</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>903</v>
+        <v>525</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
+      </c>
+      <c r="D74" t="n">
+        <v>277</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>221</v>
+        <v>662</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
+      </c>
+      <c r="D75" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
+      </c>
+      <c r="D76" t="n">
+        <v>389</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>866</v>
+        <v>585</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
+      </c>
+      <c r="D77" t="n">
+        <v>245</v>
       </c>
     </row>
     <row r="78">
@@ -1580,177 +1813,213 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>374</v>
+        <v>594</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
+      </c>
+      <c r="D78" t="n">
+        <v>482</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>807</v>
+        <v>737</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
+      </c>
+      <c r="D79" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>132</v>
+        <v>775</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
+      </c>
+      <c r="D80" t="n">
+        <v>457</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>702</v>
+        <v>302</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
+      </c>
+      <c r="D81" t="n">
+        <v>449</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>514</v>
+        <v>837</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>990</v>
+        <v>158</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
+      </c>
+      <c r="D84" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>878</v>
+        <v>67</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
+      </c>
+      <c r="D85" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>390</v>
+        <v>778</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
+      </c>
+      <c r="D86" t="n">
+        <v>402</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
+      </c>
+      <c r="D87" t="n">
+        <v>349</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>929</v>
+        <v>159</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
+      </c>
+      <c r="D88" t="n">
+        <v>429</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>899</v>
+        <v>717</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
+      </c>
+      <c r="D89" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="90">
@@ -1760,132 +2029,159 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>512</v>
+        <v>218</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
+      </c>
+      <c r="D90" t="n">
+        <v>385</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>792</v>
+        <v>43</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
+      </c>
+      <c r="D91" t="n">
+        <v>183</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>296</v>
+        <v>114</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
+      </c>
+      <c r="D92" t="n">
+        <v>315</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>237</v>
+        <v>767</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
+      </c>
+      <c r="D93" t="n">
+        <v>287</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>141</v>
+        <v>770</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
+      </c>
+      <c r="D94" t="n">
+        <v>331</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>548</v>
+        <v>408</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
+      </c>
+      <c r="D95" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>499</v>
+        <v>813</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
+      </c>
+      <c r="D96" t="n">
+        <v>407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>43</v>
+        <v>304</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
+      </c>
+      <c r="D97" t="n">
+        <v>354</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>365</v>
+        <v>58</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
+      </c>
+      <c r="D98" t="n">
+        <v>474</v>
       </c>
     </row>
     <row r="99">
@@ -1895,12 +2191,15 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>891</v>
+        <v>406</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
+      </c>
+      <c r="D99" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="100">
@@ -1910,87 +2209,105 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>804</v>
+        <v>330</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
+      </c>
+      <c r="D100" t="n">
+        <v>494</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>478</v>
+        <v>65</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
+      </c>
+      <c r="D101" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>725</v>
+        <v>267</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
+      </c>
+      <c r="D102" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>481</v>
+        <v>899</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
+      </c>
+      <c r="D103" t="n">
+        <v>399</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>715</v>
+        <v>859</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
+      </c>
+      <c r="D104" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>22</v>
+        <v>731</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
+      </c>
+      <c r="D105" t="n">
+        <v>363</v>
       </c>
     </row>
     <row r="106">
@@ -2000,57 +2317,69 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>225</v>
+        <v>386</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
+      </c>
+      <c r="D106" t="n">
+        <v>386</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>604</v>
+        <v>569</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
+      </c>
+      <c r="D107" t="n">
+        <v>378</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>343</v>
+        <v>211</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
+      </c>
+      <c r="D108" t="n">
+        <v>397</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>637</v>
+        <v>997</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
+      </c>
+      <c r="D109" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="110">
@@ -2060,1017 +2389,87 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>201</v>
+        <v>469</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
+      </c>
+      <c r="D110" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>279</v>
+        <v>86</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
+      </c>
+      <c r="D111" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>285</v>
+        <v>762</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
+      </c>
+      <c r="D112" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>991</v>
+        <v>396</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
+      </c>
+      <c r="D113" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>361</v>
+        <v>295</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>198</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>444</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>439</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>780</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>383</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>296</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>194</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>144</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>712</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>843</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>748</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>833</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>578</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>886</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>210</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>829</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>163</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>835</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>190</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>521</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>924</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>539</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>747</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>814</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>317</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>585</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>58</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>25450-P7200</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>111</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>177</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>230</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>497</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>108</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>772</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>276</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>378</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>580</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>362</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>29673-2F900</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>431</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>369</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>996</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>213</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>599</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>674</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>188</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>373</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>699</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>A6722030900</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>509</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>28674-L5500</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>467</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>400</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>303</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>25451-P7200</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>656</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>899</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>665</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>441</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>637</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>A6722031002</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>424</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>29673-2F910</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>91</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>29673-2R060</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>361</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>29696-2U000</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>331</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>28422-2M100</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>678</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>737</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>28421-2M100</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>629</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>28415-08400</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>414</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="D114" t="n">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
